--- a/tools/importer/reports/import-product-page.report.xlsx
+++ b/tools/importer/reports/import-product-page.report.xlsx
@@ -52,7 +52,7 @@
     <t>product-page</t>
   </si>
   <si>
-    <t>2026-04-16T11:58:39.707Z</t>
+    <t>2026-04-16T15:34:44.186Z</t>
   </si>
   <si>
     <t>Access Denied</t>

--- a/tools/importer/reports/import-product-page.report.xlsx
+++ b/tools/importer/reports/import-product-page.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="23">
   <si>
     <t>_reportFile</t>
   </si>
@@ -40,7 +40,7 @@
     <t>shop/p/eos-r50-rf-s18-45mm-f4-5-6-3-is-stm-lens-kit.report.json</t>
   </si>
   <si>
-    <t>[]</t>
+    <t/>
   </si>
   <si>
     <t>shop/p/eos-r50-rf-s18-45mm-f4-5-6-3-is-stm-lens-kit</t>
@@ -52,13 +52,34 @@
     <t>product-page</t>
   </si>
   <si>
-    <t>2026-04-16T15:34:44.186Z</t>
+    <t>2026-04-16T17:33:17.250Z</t>
   </si>
   <si>
     <t>Access Denied</t>
   </si>
   <si>
     <t>https://www.usa.canon.com/shop/p/eos-r50-rf-s18-45mm-f4-5-6-3-is-stm-lens-kit?color=Black&amp;type=New</t>
+  </si>
+  <si>
+    <t>business/it-and-security/five-pillars-of-security/device-security.report.json</t>
+  </si>
+  <si>
+    <t>["hero-security","tabs-pillar-nav","columns-content-split","columns-content-split","accordion-resources","cards-bumper"]</t>
+  </si>
+  <si>
+    <t>business/it-and-security/five-pillars-of-security/device-security</t>
+  </si>
+  <si>
+    <t>security-pillar-page</t>
+  </si>
+  <si>
+    <t>2026-04-16T15:20:02.821Z</t>
+  </si>
+  <si>
+    <t>Device Security | Canon U.S.A., Inc.</t>
+  </si>
+  <si>
+    <t>https://www.usa.canon.com/business/it-and-security/five-pillars-of-security/device-security</t>
   </si>
 </sst>
 </file>
@@ -447,15 +468,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="50" customWidth="1"/>
-    <col min="2" max="2" width="8" customWidth="1"/>
-    <col min="3" max="3" width="50" customWidth="1"/>
-    <col min="5" max="5" width="14" customWidth="1"/>
+    <col min="1" max="3" width="50" customWidth="1"/>
+    <col min="5" max="5" width="22" customWidth="1"/>
     <col min="6" max="6" width="26" customWidth="1"/>
-    <col min="7" max="7" width="15" customWidth="1"/>
+    <col min="7" max="7" width="38" customWidth="1"/>
     <col min="8" max="8" width="50" customWidth="1"/>
   </cols>
   <sheetData>
@@ -509,6 +528,32 @@
       </c>
       <c r="H2" t="s">
         <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H3" t="s">
+        <v>22</v>
       </c>
     </row>
   </sheetData>
